--- a/artfynd/A 56299-2021 artfynd.xlsx
+++ b/artfynd/A 56299-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56299-2021 artfynd.xlsx
+++ b/artfynd/A 56299-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1412,6 +1412,122 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130801667</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92197</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hökebo S, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>561294</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6634808</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-01-20</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På torrgren i kronan.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56299-2021 artfynd.xlsx
+++ b/artfynd/A 56299-2021 artfynd.xlsx
@@ -1417,7 +1417,7 @@
         <v>130801667</v>
       </c>
       <c r="B8" t="n">
-        <v>92197</v>
+        <v>92198</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56299-2021 artfynd.xlsx
+++ b/artfynd/A 56299-2021 artfynd.xlsx
@@ -1417,7 +1417,7 @@
         <v>130801667</v>
       </c>
       <c r="B8" t="n">
-        <v>92198</v>
+        <v>92199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56299-2021 artfynd.xlsx
+++ b/artfynd/A 56299-2021 artfynd.xlsx
@@ -1417,7 +1417,7 @@
         <v>130801667</v>
       </c>
       <c r="B8" t="n">
-        <v>92199</v>
+        <v>92207</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56299-2021 artfynd.xlsx
+++ b/artfynd/A 56299-2021 artfynd.xlsx
@@ -675,66 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>68895609</v>
+        <v>130801667</v>
       </c>
       <c r="B2" t="n">
-        <v>6203</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>101520</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Större flatbagge</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Peltis grossa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hökebo, S, Vstm</t>
+          <t>Hökebo S, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561179.6784116243</v>
+        <v>561294</v>
       </c>
       <c r="R2" t="n">
-        <v>6634971.387725323</v>
+        <v>6634808</v>
       </c>
       <c r="S2" t="n">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,27 +743,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-01-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-01-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>under bark på björklåga</t>
+          <t>På torrgren i kronan.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,33 +762,39 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Tall</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Hanna Lundmark</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68895651</v>
+        <v>70848477</v>
       </c>
       <c r="B3" t="n">
-        <v>8367</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,50 +802,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>6456</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hökebo, S, Vstm</t>
+          <t>Bovallen, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561179.6784116243</v>
+        <v>561398</v>
       </c>
       <c r="R3" t="n">
-        <v>6634971.387725323</v>
+        <v>6634675</v>
       </c>
       <c r="S3" t="n">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,27 +856,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-01-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-04-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-01-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Under bark på björk</t>
+          <t>2018-04-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,62 +876,62 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ralf Lundmark, Hanna Lundmark</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>70848477</v>
+        <v>70848476</v>
       </c>
       <c r="B4" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bovallen, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561398.0440187291</v>
+        <v>561366</v>
       </c>
       <c r="R4" t="n">
-        <v>6634674.931098104</v>
+        <v>6634736</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,19 +961,9 @@
           <t>2018-04-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2018-04-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1047,53 +990,61 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>70848478</v>
+        <v>68895609</v>
       </c>
       <c r="B5" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>6275</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>101520</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Större flatbagge</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Peltis grossa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bovallen, Vstm</t>
+          <t>Hökebo, S, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561423.2237637327</v>
+        <v>561180</v>
       </c>
       <c r="R5" t="n">
-        <v>6634644.184005496</v>
+        <v>6634971</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>88</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,22 +1068,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2018-04-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-01-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2018-04-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-01-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>under bark på björklåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,63 +1089,43 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Ralf Lundmark, Hanna Lundmark</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>70848476</v>
+        <v>68897194</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1207,25 +1133,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bovallen, Vstm</t>
+          <t>Hökebo, S, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561365.8145010817</v>
+        <v>561180</v>
       </c>
       <c r="R6" t="n">
-        <v>6634736.221984747</v>
+        <v>6634971</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>88</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1249,22 +1181,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2018-04-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-01-04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2018-04-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-01-04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,70 +1201,73 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jacob Rudhe</t>
+          <t>Ralf Lundmark, Hanna Lundmark, Lotta Lundmark</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104459183</v>
+        <v>68895651</v>
       </c>
       <c r="B7" t="n">
-        <v>6203</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101520</v>
+        <v>106554</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Större flatbagge</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Peltis grossa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Virsbo-Näs, Vstm</t>
+          <t>Hökebo, S, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561129.8738372191</v>
+        <v>561180</v>
       </c>
       <c r="R7" t="n">
-        <v>6634999.717663046</v>
+        <v>6634971</v>
       </c>
       <c r="S7" t="n">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1366,58 +1291,47 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-01-04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-11-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-01-04</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Gnag och kläckhål eftersöktes eftersom arten tidigare är rapporterad från platsen (2018). Dessvärre utan framgång. Gott om klibbtickeangripna granar och brutna stubbar gör att platsen definitivt har potential, inte minst om några år. Kanske gynnas arten på sikt också av senare års intensivare svärmningar av Ips typographus som torde resultera i lämpliga substrat.</t>
+          <t>Under bark på björk</t>
         </is>
       </c>
       <c r="AD7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Erik Berg</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Erik Berg, Ylva Norén</t>
+          <t>Ralf Lundmark, Hanna Lundmark</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130801667</v>
+        <v>70848478</v>
       </c>
       <c r="B8" t="n">
-        <v>92231</v>
+        <v>80392</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1425,40 +1339,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4217</v>
+        <v>229497</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hökebo S, Vstm</t>
+          <t>Bovallen, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561294</v>
+        <v>561423</v>
       </c>
       <c r="R8" t="n">
-        <v>6634808</v>
+        <v>6634644</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1482,17 +1393,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2018-04-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På torrgren i kronan.</t>
+          <t>2018-04-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1501,29 +1407,33 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Barrblandskog.</t>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Jacob Rudhe</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 56299-2021 artfynd.xlsx
+++ b/artfynd/A 56299-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130801667</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70848477</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70848476</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68895609</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68897194</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1325,6 +1355,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68895651</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1437,8 +1472,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70848478</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>